--- a/slide_classification/SurGen_Results/Caption_based_aggregation/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/SurGen_Results/Caption_based_aggregation/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,19 +468,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9102564102564102</v>
+        <v>0.8910256410256411</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.8859060402684564</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9096774193548387</v>
+        <v>0.8895705521472392</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.8831168831168831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.903494623655914</v>
+        <v>0.887404779139555</v>
       </c>
     </row>
     <row r="3">
@@ -489,19 +490,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6226950354609929</v>
+        <v>0.7178571428571429</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7191489361702128</v>
+        <v>0.5529100529100529</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6226190476190476</v>
+        <v>0.5497747747747748</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6081534772182254</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6339728976697061</v>
+        <v>0.607173861940049</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +512,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6576802507836991</v>
+        <v>0.7119582926034539</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7482517482517482</v>
+        <v>0.5645521746604779</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6575126262626263</v>
+        <v>0.5613038277511961</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5801733477789816</v>
+        <v>0.6219312602291326</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6609044932692637</v>
+        <v>0.6149363888110652</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8951772365565471</v>
+        <v>0.8924814731266344</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9176976869284561</v>
+        <v>0.8683320007430201</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8945096122515477</v>
+        <v>0.8709454897701587</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8619508614965224</v>
+        <v>0.8749548324016408</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8923338493082683</v>
+        <v>0.8766784490103634</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +556,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8600472813238771</v>
+        <v>0.8566964285714286</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8468085106382979</v>
+        <v>0.6063492063492064</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8380952380952381</v>
+        <v>0.7851351351351352</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7876190476190477</v>
+        <v>0.8465227817745804</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8331425194191152</v>
+        <v>0.7736758879575876</v>
       </c>
     </row>
     <row r="7">
@@ -578,31 +579,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[[138   3]
- [ 11   4]]</t>
+          <t>[[131, 9], [8, 8]]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[[137   4]
- [  8   7]]</t>
+          <t>[[130, 5], [12, 2]]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[[137   3]
- [ 11   4]]</t>
+          <t>[[143, 5], [13, 2]]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[[132   8]
- [ 12   3]]</t>
+          <t>[[132, 7], [11, 4]]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[[136, 4], [10, 4]]</t>
+          <t>[[134, 6], [11, 4]]</t>
         </is>
       </c>
     </row>
@@ -613,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7756410256410257</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8012820512820513</v>
+        <v>0.7651006711409396</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.7852760736196319</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8129032258064516</v>
+        <v>0.7792207792207793</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8215570719602978</v>
+        <v>0.776309637405594</v>
       </c>
     </row>
     <row r="9">
@@ -635,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7886524822695036</v>
+        <v>0.6535714285714286</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7411347517730495</v>
+        <v>0.6142857142857143</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8511904761904763</v>
+        <v>0.6421171171171172</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6583333333333333</v>
+        <v>0.6992805755395683</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7598277608915907</v>
+        <v>0.6523137088784571</v>
       </c>
     </row>
     <row r="10">
@@ -657,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6799242424242424</v>
+        <v>0.5898129366689204</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6366914581924724</v>
+        <v>0.5579384589302365</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7066394125217654</v>
+        <v>0.5796802475502836</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6084835815695497</v>
+        <v>0.6066706730769231</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6579346736770075</v>
+        <v>0.583525579056591</v>
       </c>
     </row>
     <row r="11">
@@ -679,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8589015151515152</v>
+        <v>0.8092670607883589</v>
       </c>
       <c r="C11" t="n">
-        <v>0.834200169899967</v>
+        <v>0.8036897106703843</v>
       </c>
       <c r="D11" t="n">
-        <v>0.865377711677522</v>
+        <v>0.8195420446311898</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8366305059410921</v>
+        <v>0.8164374687812188</v>
       </c>
       <c r="F11" t="n">
-        <v>0.848777475667524</v>
+        <v>0.812234071217788</v>
       </c>
     </row>
     <row r="12">
@@ -701,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8463356973995272</v>
+        <v>0.7741071428571429</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8146572104018913</v>
+        <v>0.5888888888888889</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9042857142857144</v>
+        <v>0.6995495495495496</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7233333333333333</v>
+        <v>0.7443645083932854</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8221529888551166</v>
+        <v>0.7017275224222167</v>
       </c>
     </row>
     <row r="13">
@@ -724,31 +721,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[119  22]
- [  4  11]]</t>
+          <t>[[113, 27], [8, 8]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[115  26]
- [  5  10]]</t>
+          <t>[[108, 27], [8, 6]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[117  23]
- [  2  13]]</t>
+          <t>[[121, 27], [8, 7]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[119  21]
- [  8   7]]</t>
+          <t>[[111, 28], [6, 9]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[118, 23], [5, 10]]</t>
+          <t>[[113, 27], [8, 8]]</t>
         </is>
       </c>
     </row>
@@ -759,19 +752,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9038461538461539</v>
+        <v>0.8910256410256411</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9038461538461539</v>
+        <v>0.8993288590604027</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.8834355828220859</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8903225806451613</v>
+        <v>0.9025974025974026</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9003101736972705</v>
+        <v>0.8940968713763831</v>
       </c>
     </row>
     <row r="15">
@@ -781,19 +774,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5297872340425532</v>
+        <v>0.4964285714285714</v>
       </c>
       <c r="C15" t="n">
+        <v>0.4962962962962963</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.4864864864864865</v>
+      </c>
+      <c r="E15" t="n">
         <v>0.5</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.4928571428571429</v>
-      </c>
       <c r="F15" t="n">
-        <v>0.505661094224924</v>
+        <v>0.4948028385528386</v>
       </c>
     </row>
     <row r="16">
@@ -803,19 +796,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5333998005982054</v>
+        <v>0.4711864406779661</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4747474747474748</v>
+        <v>0.4734982332155477</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4745762711864407</v>
+        <v>0.4690553745928339</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4709897610921502</v>
+        <v>0.4744027303754266</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4884283269060677</v>
+        <v>0.4720356947154435</v>
       </c>
     </row>
     <row r="17">
@@ -825,19 +818,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8692000920315974</v>
+        <v>0.8457192524989134</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8581973581973582</v>
+        <v>0.858016932672469</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8572990705303446</v>
+        <v>0.851781539137907</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8508202135858196</v>
+        <v>0.8563893444439519</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8588791835862799</v>
+        <v>0.8529767671883104</v>
       </c>
     </row>
     <row r="18">
@@ -847,19 +840,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6659574468085105</v>
+        <v>0.6540178571428572</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6697399527186761</v>
+        <v>0.6349206349206349</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6497619047619049</v>
+        <v>0.5878378378378378</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6378571428571429</v>
+        <v>0.6316546762589927</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6558291117865586</v>
+        <v>0.6271077515400807</v>
       </c>
     </row>
     <row r="19">
@@ -870,31 +863,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[140   1]
- [ 14   1]]</t>
+          <t>[[139, 1], [16, 0]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[141   0]
- [ 15   0]]</t>
+          <t>[[134, 1], [14, 0]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[140   0]
- [ 15   0]]</t>
+          <t>[[144, 4], [15, 0]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[138   2]
- [ 15   0]]</t>
+          <t>[[139, 0], [15, 0]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[140, 1], [15, 0]]</t>
+          <t>[[139, 2], [15, 0]]</t>
         </is>
       </c>
     </row>
@@ -905,19 +894,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6410256410256411</v>
+        <v>0.7115384615384616</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.697986577181208</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7354838709677419</v>
+        <v>0.6380368098159509</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6580645161290323</v>
+        <v>0.6688311688311688</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6753101736972705</v>
+        <v>0.6790982543416972</v>
       </c>
     </row>
     <row r="21">
@@ -927,19 +916,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5929078014184397</v>
+        <v>0.6455357142857143</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5773049645390071</v>
+        <v>0.6412698412698412</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7047619047619047</v>
+        <v>0.5909909909909909</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6023809523809524</v>
+        <v>0.6083932853717027</v>
       </c>
       <c r="F21" t="n">
-        <v>0.619338905775076</v>
+        <v>0.6215474579795623</v>
       </c>
     </row>
     <row r="22">
@@ -949,19 +938,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4944444444444445</v>
+        <v>0.5524956970740103</v>
       </c>
       <c r="C22" t="n">
-        <v>0.500369549150037</v>
+        <v>0.536210832122847</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5816051089604318</v>
+        <v>0.489136786188579</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5059835227614409</v>
+        <v>0.5135938564439214</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5206006563290886</v>
+        <v>0.5228592929573393</v>
       </c>
     </row>
     <row r="23">
@@ -971,19 +960,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7143162393162393</v>
+        <v>0.7645527163599452</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7331855136733185</v>
+        <v>0.7586524815780934</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7862311222680249</v>
+        <v>0.7141788673526752</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7270314782375912</v>
+        <v>0.7348516350188488</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7401910883737934</v>
+        <v>0.7430589250773907</v>
       </c>
     </row>
     <row r="24">
@@ -993,19 +982,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6127659574468085</v>
+        <v>0.6986607142857142</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6463356973995271</v>
+        <v>0.698941798941799</v>
       </c>
       <c r="D24" t="n">
-        <v>0.799047619047619</v>
+        <v>0.6558558558558558</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6447619047619048</v>
+        <v>0.6043165467625899</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6757277946639649</v>
+        <v>0.6644437289614897</v>
       </c>
     </row>
     <row r="25">
@@ -1016,31 +1005,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[[92 49]
- [ 7  8]]</t>
+          <t>[[102, 38], [7, 9]]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[[97 44]
- [ 8  7]]</t>
+          <t>[[96, 39], [6, 8]]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[[104  36]
- [  5  10]]</t>
+          <t>[[96, 52], [7, 8]]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[[94 46]
- [ 7  8]]</t>
+          <t>[[95, 44], [7, 8]]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[[97, 44], [7, 8]]</t>
+          <t>[[97, 43], [7, 8]]</t>
         </is>
       </c>
     </row>
@@ -1051,19 +1036,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.8910256410256411</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9038461538461539</v>
+        <v>0.8926174496644296</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9096774193548387</v>
+        <v>0.901840490797546</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8903225806451613</v>
+        <v>0.8831168831168831</v>
       </c>
       <c r="F26" t="n">
-        <v>0.900320512820513</v>
+        <v>0.8921501161511249</v>
       </c>
     </row>
     <row r="27">
@@ -1073,19 +1058,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4964539007092199</v>
+        <v>0.5241071428571429</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5297872340425532</v>
+        <v>0.4925925925925926</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5630952380952381</v>
+        <v>0.4966216216216216</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5226190476190476</v>
+        <v>0.4892086330935252</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5279888551165147</v>
+        <v>0.5006324975412205</v>
       </c>
     </row>
     <row r="28">
@@ -1095,19 +1080,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.472972972972973</v>
+        <v>0.5236213400395187</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5333998005982054</v>
+        <v>0.4716312056737589</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5871385083713851</v>
+        <v>0.4741935483870968</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5234219569542413</v>
+        <v>0.4689655172413793</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5292333097242012</v>
+        <v>0.4846029028354384</v>
       </c>
     </row>
     <row r="29">
@@ -1117,19 +1102,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8549896049896051</v>
+        <v>0.8561624591802425</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8692000920315974</v>
+        <v>0.8546337284021135</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8814258359110325</v>
+        <v>0.8611122105679794</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8606467949054544</v>
+        <v>0.8465741155396328</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8665655819594223</v>
+        <v>0.8546206284224921</v>
       </c>
     </row>
     <row r="30">
@@ -1139,19 +1124,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8505910165484634</v>
+        <v>0.8165178571428572</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7782505910165485</v>
+        <v>0.6878306878306878</v>
       </c>
       <c r="D30" t="n">
-        <v>0.87</v>
+        <v>0.7932432432432432</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7276190476190476</v>
+        <v>0.7702637889688249</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8066151637960148</v>
+        <v>0.7669638942964033</v>
       </c>
     </row>
     <row r="31">
@@ -1162,31 +1147,413 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[[140   1]
- [ 15   0]]</t>
+          <t>[[138, 2], [15, 1]]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[[140   1]
- [ 14   1]]</t>
+          <t>[[133, 2], [14, 0]]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[[139   1]
- [ 13   2]]</t>
+          <t>[[147, 1], [15, 0]]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[[137   3]
- [ 14   1]]</t>
+          <t>[[136, 3], [15, 0]]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[[139, 2], [14, 1]]</t>
+          <t>[[138, 2], [15, 0]]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Classifier</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>N_folds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>N_test</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>acc_sd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bacc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bacc_sd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_sd</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1_sd</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>auroc</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>auroc_sd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>conf_matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Caption_based_aggregation</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.887404779139555</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.003099737247893439</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.607173861940049</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.06799074293335119</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6149363888110652</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.06098606128261532</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8766784490103634</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.009423858628006276</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.7736758879575876</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1004099258372241</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>[[134, 6], [11, 4]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Caption_based_aggregation</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>622</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.776309637405594</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.007330751862230953</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6523137088784571</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.03064949950277243</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.583525579056591</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.01764024896160217</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.812234071217788</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.006182319033736741</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.7017275224222167</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.07034561608676089</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[[113, 27], [8, 8]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Caption_based_aggregation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>knn</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>622</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8940968713763831</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.007462041538187926</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4948028385528386</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.005026072577423443</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4720356947154435</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.002082391481765756</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8529767671883104</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.004773600349649865</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.6271077515400807</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02422806005880258</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[[139, 2], [15, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Caption_based_aggregation</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>proto</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>622</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6790982543416972</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.02828688324153102</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6215474579795623</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.02275488285555064</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5228592929573393</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.02387276598766876</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7430589250773907</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.02004095439547828</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6644437289614897</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0388907075041798</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[[97, 43], [7, 8]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Caption_based_aggregation</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>622</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8921501161511249</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.006651794959997801</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5006324975412205</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.01380480757610427</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4846029028354384</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.02260301892088519</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8546206284224921</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.005226481178112121</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.7669638942964033</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.04852616069001375</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>[[138, 2], [15, 0]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/SurGen_Results/Caption_based_aggregation/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/SurGen_Results/Caption_based_aggregation/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
